--- a/v2/uploads/Vector Ajuste Data Histórica.xlsx
+++ b/v2/uploads/Vector Ajuste Data Histórica.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aminerals-my.sharepoint.com/personal/mmadrida_pelambres_cl1/Documents/Documentos/Control Gestión 2026/Presupuesto Corporativo/Vector Ajuste/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="205" documentId="11_AD4D2F04E46CFB4ACB3E20581593C05A683EDF21" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2CD26C01-9ED0-496E-B13C-4003ECC8E158}"/>
+  <xr:revisionPtr revIDLastSave="234" documentId="11_AD4D2F04E46CFB4ACB3E20581593C05A683EDF21" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B02098D0-971A-4AB6-BAE9-644764F44D58}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
